--- a/salidas/empresas/LLY.xlsx
+++ b/salidas/empresas/LLY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>31.53524208068848</v>
+        <v>31.53523826599121</v>
       </c>
       <c r="C2" t="n">
         <v>56.61999893188477</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>31.2004222869873</v>
+        <v>31.20042037963867</v>
       </c>
       <c r="C3" t="n">
         <v>55.61999893188477</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>31.02093124389648</v>
+        <v>31.02091407775879</v>
       </c>
       <c r="C4" t="n">
         <v>55.29999923706055</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>29.68583679199219</v>
+        <v>29.68583869934082</v>
       </c>
       <c r="C5" t="n">
         <v>52.91999816894531</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>29.19210052490234</v>
+        <v>29.19211196899414</v>
       </c>
       <c r="C6" t="n">
         <v>51.63999938964844</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>31.24413871765137</v>
+        <v>31.24416351318359</v>
       </c>
       <c r="C7" t="n">
         <v>55.27000045776367</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>32.09209823608398</v>
+        <v>32.09209442138672</v>
       </c>
       <c r="C8" t="n">
         <v>56.77000045776367</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>31.84765243530273</v>
+        <v>31.84764862060547</v>
       </c>
       <c r="C9" t="n">
         <v>55.93000030517578</v>
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>31.89322662353516</v>
+        <v>31.8931999206543</v>
       </c>
       <c r="C11" t="n">
         <v>56.0099983215332</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>30.74234580993652</v>
+        <v>30.74232864379883</v>
       </c>
       <c r="C12" t="n">
         <v>53.59000015258789</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>29.88760185241699</v>
+        <v>29.88758087158203</v>
       </c>
       <c r="C13" t="n">
         <v>52.09999847412109</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>31.04638862609863</v>
+        <v>31.04638290405273</v>
       </c>
       <c r="C14" t="n">
         <v>54.11999893188477</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>30.40619277954102</v>
+        <v>30.40618324279785</v>
       </c>
       <c r="C15" t="n">
         <v>52.59000015258789</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>31.05375862121582</v>
+        <v>31.05374336242676</v>
       </c>
       <c r="C16" t="n">
         <v>53.70999908447266</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>34.18744659423828</v>
+        <v>34.18743896484375</v>
       </c>
       <c r="C17" t="n">
         <v>59.13000106811523</v>
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>32.5439567565918</v>
+        <v>32.54397201538086</v>
       </c>
       <c r="C19" t="n">
         <v>55.88000106811523</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>31.50148582458496</v>
+        <v>31.50147819519043</v>
       </c>
       <c r="C20" t="n">
         <v>54.09000015258789</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>33.65027236938477</v>
+        <v>33.65027618408203</v>
       </c>
       <c r="C21" t="n">
         <v>57.34999847412109</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>33.40384292602539</v>
+        <v>33.40383148193359</v>
       </c>
       <c r="C22" t="n">
         <v>56.93000030517578</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>31.77266883850098</v>
+        <v>31.77266693115234</v>
       </c>
       <c r="C23" t="n">
         <v>54.15000152587891</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>31.3221263885498</v>
+        <v>31.32210731506348</v>
       </c>
       <c r="C24" t="n">
         <v>52.95000076293945</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>31.58240127563477</v>
+        <v>31.58240699768066</v>
       </c>
       <c r="C25" t="n">
         <v>53.38999938964844</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>30.39932060241699</v>
+        <v>30.39932441711426</v>
       </c>
       <c r="C26" t="n">
         <v>51.38999938964844</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>29.86401748657227</v>
+        <v>29.8640308380127</v>
       </c>
       <c r="C27" t="n">
         <v>50.02000045776367</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>30.80136108398438</v>
+        <v>30.80137825012207</v>
       </c>
       <c r="C28" t="n">
         <v>51.59000015258789</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>28.7415828704834</v>
+        <v>28.74158477783203</v>
       </c>
       <c r="C29" t="n">
         <v>48.13999938964844</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>29.02131080627441</v>
+        <v>29.02132225036621</v>
       </c>
       <c r="C30" t="n">
         <v>48.13999938964844</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>27.82767105102539</v>
+        <v>27.82767868041992</v>
       </c>
       <c r="C31" t="n">
         <v>46.15999984741211</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>28.40038108825684</v>
+        <v>28.4003849029541</v>
       </c>
       <c r="C32" t="n">
         <v>47.11000061035156</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>28.3940372467041</v>
+        <v>28.3940258026123</v>
       </c>
       <c r="C33" t="n">
         <v>46.65000152587891</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>26.79935264587402</v>
+        <v>26.79933929443359</v>
       </c>
       <c r="C34" t="n">
         <v>44.02999877929688</v>
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>24.85466384887695</v>
+        <v>24.85466766357422</v>
       </c>
       <c r="C37" t="n">
         <v>40.27000045776367</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>22.72532272338867</v>
+        <v>22.72532081604004</v>
       </c>
       <c r="C38" t="n">
         <v>36.81999969482422</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>18.37711715698242</v>
+        <v>18.37711334228516</v>
       </c>
       <c r="C39" t="n">
         <v>29.3799991607666</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>20.89787101745605</v>
+        <v>20.89786911010742</v>
       </c>
       <c r="C40" t="n">
         <v>33.40999984741211</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>20.59137153625488</v>
+        <v>20.59137535095215</v>
       </c>
       <c r="C41" t="n">
         <v>32.91999816894531</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>21.92267227172852</v>
+        <v>21.92266464233398</v>
       </c>
       <c r="C42" t="n">
         <v>34.56999969482422</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>21.96706771850586</v>
+        <v>21.96706390380859</v>
       </c>
       <c r="C43" t="n">
         <v>34.63999938964844</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>22.12559700012207</v>
+        <v>22.12558937072754</v>
       </c>
       <c r="C44" t="n">
         <v>34.88999938964844</v>
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>21.53211402893066</v>
+        <v>21.5321159362793</v>
       </c>
       <c r="C45" t="n">
         <v>33.45999908447266</v>
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>21.25541305541992</v>
+        <v>21.25540161132812</v>
       </c>
       <c r="C46" t="n">
         <v>33.02999877929688</v>
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>21.88604545593262</v>
+        <v>21.88605117797852</v>
       </c>
       <c r="C47" t="n">
         <v>34.0099983215332</v>
@@ -1380,11 +1392,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>23.96894836425781</v>
+        <v>23.96894073486328</v>
       </c>
       <c r="C48" t="n">
         <v>36.72999954223633</v>
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>23.30333137512207</v>
+        <v>23.30331993103027</v>
       </c>
       <c r="C49" t="n">
         <v>35.70999908447266</v>
@@ -1430,11 +1442,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>22.97051048278809</v>
+        <v>22.97051620483398</v>
       </c>
       <c r="C50" t="n">
         <v>35.20000076293945</v>
@@ -1455,7 +1467,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>23.96980667114258</v>
+        <v>23.96981620788574</v>
       </c>
       <c r="C52" t="n">
         <v>36.22000122070312</v>
@@ -1505,7 +1517,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>22.00551414489746</v>
+        <v>22.00551605224609</v>
       </c>
       <c r="C54" t="n">
         <v>32.79000091552734</v>
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>22.48200225830078</v>
+        <v>22.48200988769531</v>
       </c>
       <c r="C55" t="n">
         <v>33.5</v>
@@ -1580,11 +1592,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>23.89131927490234</v>
+        <v>23.89133071899414</v>
       </c>
       <c r="C56" t="n">
         <v>35.59999847412109</v>
@@ -1605,11 +1617,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>22.83870124816895</v>
+        <v>22.83869743347168</v>
       </c>
       <c r="C57" t="n">
         <v>33.59000015258789</v>
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>24.83768463134766</v>
+        <v>24.83767509460449</v>
       </c>
       <c r="C58" t="n">
         <v>36.52999877929688</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>23.93338203430176</v>
+        <v>23.93338012695312</v>
       </c>
       <c r="C59" t="n">
         <v>35.20000076293945</v>
@@ -1680,11 +1692,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>23.20415496826172</v>
+        <v>23.20416259765625</v>
       </c>
       <c r="C60" t="n">
         <v>33.65999984741211</v>
@@ -1705,11 +1717,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>24.15549087524414</v>
+        <v>24.15548706054688</v>
       </c>
       <c r="C61" t="n">
         <v>35.04000091552734</v>
@@ -1730,11 +1742,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>23.96934700012207</v>
+        <v>23.96935653686523</v>
       </c>
       <c r="C62" t="n">
         <v>34.77000045776367</v>
@@ -1755,11 +1767,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>24.15690422058105</v>
+        <v>24.15689849853516</v>
       </c>
       <c r="C63" t="n">
         <v>34.56000137329102</v>
@@ -1780,7 +1792,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
@@ -1805,11 +1817,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>25.86940574645996</v>
+        <v>25.86941719055176</v>
       </c>
       <c r="C65" t="n">
         <v>37.0099983215332</v>
@@ -1830,11 +1842,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>27.24165534973145</v>
+        <v>27.24166488647461</v>
       </c>
       <c r="C66" t="n">
         <v>38.47999954223633</v>
@@ -1855,11 +1867,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>26.56911087036133</v>
+        <v>26.56911849975586</v>
       </c>
       <c r="C67" t="n">
         <v>37.52999877929688</v>
@@ -1880,11 +1892,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>27.11422729492188</v>
+        <v>27.11423492431641</v>
       </c>
       <c r="C68" t="n">
         <v>38.29999923706055</v>
@@ -1905,11 +1917,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>26.93765068054199</v>
+        <v>26.93766593933105</v>
       </c>
       <c r="C69" t="n">
         <v>37.5099983215332</v>
@@ -1930,11 +1942,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>26.54986381530762</v>
+        <v>26.54986190795898</v>
       </c>
       <c r="C70" t="n">
         <v>36.97000122070312</v>
@@ -1955,7 +1967,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -1984,11 +1996,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>27.53833389282227</v>
+        <v>27.53832817077637</v>
       </c>
       <c r="C72" t="n">
         <v>37.84999847412109</v>
@@ -2013,11 +2025,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>30.23760032653809</v>
+        <v>30.23759460449219</v>
       </c>
       <c r="C73" t="n">
         <v>41.56000137329102</v>
@@ -2042,7 +2054,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2071,11 +2083,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>28.91001892089844</v>
+        <v>28.91002464294434</v>
       </c>
       <c r="C75" t="n">
         <v>39.2400016784668</v>
@@ -2100,11 +2112,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>29.66886520385742</v>
+        <v>29.66886329650879</v>
       </c>
       <c r="C76" t="n">
         <v>40.27000045776367</v>
@@ -2129,11 +2141,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>30.49402236938477</v>
+        <v>30.4940071105957</v>
       </c>
       <c r="C77" t="n">
         <v>41.38999938964844</v>
@@ -2158,11 +2170,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>30.52814483642578</v>
+        <v>30.52815818786621</v>
       </c>
       <c r="C78" t="n">
         <v>40.95000076293945</v>
@@ -2187,11 +2199,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>31.98933410644531</v>
+        <v>31.98932838439941</v>
       </c>
       <c r="C79" t="n">
         <v>42.90999984741211</v>
@@ -2216,11 +2228,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>32.82427215576172</v>
+        <v>32.82430267333984</v>
       </c>
       <c r="C80" t="n">
         <v>44.02999877929688</v>
@@ -2245,7 +2257,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2274,11 +2286,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>35.74578475952148</v>
+        <v>35.74581527709961</v>
       </c>
       <c r="C82" t="n">
         <v>47.40999984741211</v>
@@ -2303,11 +2315,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>36.66563034057617</v>
+        <v>36.66563415527344</v>
       </c>
       <c r="C83" t="n">
         <v>48.63000106811523</v>
@@ -2328,11 +2340,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>37.35371780395508</v>
+        <v>37.35372161865234</v>
       </c>
       <c r="C84" t="n">
         <v>49.04000091552734</v>
@@ -2353,11 +2365,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>37.56699371337891</v>
+        <v>37.56700134277344</v>
       </c>
       <c r="C85" t="n">
         <v>49.31999969482422</v>
@@ -2378,11 +2390,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>40.89562606811523</v>
+        <v>40.89561462402344</v>
       </c>
       <c r="C86" t="n">
         <v>53.68999862670898</v>
@@ -2403,11 +2415,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>42.01714324951172</v>
+        <v>42.01715850830078</v>
       </c>
       <c r="C87" t="n">
         <v>54.65999984741211</v>
@@ -2428,11 +2440,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>43.65447998046875</v>
+        <v>43.65449905395508</v>
       </c>
       <c r="C88" t="n">
         <v>56.79000091552734</v>
@@ -2453,11 +2465,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>42.57062911987305</v>
+        <v>42.57062530517578</v>
       </c>
       <c r="C89" t="n">
         <v>55.38000106811523</v>
@@ -2478,11 +2490,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>41.22300720214844</v>
+        <v>41.2230110168457</v>
       </c>
       <c r="C90" t="n">
         <v>53.15999984741211</v>
@@ -2503,11 +2515,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>38.09017562866211</v>
+        <v>38.09018707275391</v>
       </c>
       <c r="C91" t="n">
         <v>49.11999893188477</v>
@@ -2528,11 +2540,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>41.18424224853516</v>
+        <v>41.18422698974609</v>
       </c>
       <c r="C92" t="n">
         <v>53.11000061035156</v>
@@ -2553,11 +2565,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>40.22288131713867</v>
+        <v>40.22286987304688</v>
       </c>
       <c r="C93" t="n">
         <v>51.40000152587891</v>
@@ -2578,11 +2590,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>39.38554382324219</v>
+        <v>39.38553237915039</v>
       </c>
       <c r="C94" t="n">
         <v>50.33000183105469</v>
@@ -2603,7 +2615,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2628,11 +2640,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>39.68794250488281</v>
+        <v>39.68793106079102</v>
       </c>
       <c r="C96" t="n">
         <v>50.22000122070312</v>
@@ -2653,11 +2665,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>40.30435943603516</v>
+        <v>40.30435180664062</v>
       </c>
       <c r="C97" t="n">
         <v>51</v>
@@ -2678,11 +2690,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>42.68310546875</v>
+        <v>42.68309783935547</v>
       </c>
       <c r="C98" t="n">
         <v>54.0099983215332</v>
@@ -2703,11 +2715,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>47.5359992980957</v>
+        <v>47.53599166870117</v>
       </c>
       <c r="C99" t="n">
         <v>59.61000061035156</v>
@@ -2732,11 +2744,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>46.93789291381836</v>
+        <v>46.93790435791016</v>
       </c>
       <c r="C100" t="n">
         <v>58.86000061035156</v>
@@ -2761,11 +2773,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>47.1292839050293</v>
+        <v>47.12929534912109</v>
       </c>
       <c r="C101" t="n">
         <v>59.09999847412109</v>
@@ -2790,11 +2802,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>48.13225555419922</v>
+        <v>48.13225936889648</v>
       </c>
       <c r="C102" t="n">
         <v>59.86000061035156</v>
@@ -2819,11 +2831,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>49.98968887329102</v>
+        <v>49.98969268798828</v>
       </c>
       <c r="C103" t="n">
         <v>62.16999816894531</v>
@@ -2848,11 +2860,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>49.09716415405273</v>
+        <v>49.09717178344727</v>
       </c>
       <c r="C104" t="n">
         <v>61.06000137329102</v>
@@ -2877,11 +2889,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>51.51871109008789</v>
+        <v>51.51869964599609</v>
       </c>
       <c r="C105" t="n">
         <v>63.56000137329102</v>
@@ -2906,11 +2918,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>52.56432723999023</v>
+        <v>52.56430435180664</v>
       </c>
       <c r="C106" t="n">
         <v>64.84999847412109</v>
@@ -2935,11 +2947,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>53.76392364501953</v>
+        <v>53.76394271850586</v>
       </c>
       <c r="C107" t="n">
         <v>66.33000183105469</v>
@@ -2964,11 +2976,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>55.61650085449219</v>
+        <v>55.61649322509766</v>
       </c>
       <c r="C108" t="n">
         <v>68.12000274658203</v>
@@ -2993,7 +3005,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3022,11 +3034,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>58.78427886962891</v>
+        <v>58.7842903137207</v>
       </c>
       <c r="C110" t="n">
         <v>72</v>
@@ -3051,7 +3063,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3080,11 +3092,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>59.7386589050293</v>
+        <v>59.73866271972656</v>
       </c>
       <c r="C112" t="n">
         <v>72.65000152587891</v>
@@ -3109,11 +3121,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>59.0973014831543</v>
+        <v>59.0972900390625</v>
       </c>
       <c r="C113" t="n">
         <v>71.87000274658203</v>
@@ -3138,7 +3150,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3167,7 +3179,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3196,7 +3208,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3225,11 +3237,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>68.59359741210938</v>
+        <v>68.5936279296875</v>
       </c>
       <c r="C117" t="n">
         <v>82.34999847412109</v>
@@ -3254,11 +3266,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>69.70977020263672</v>
+        <v>69.70979309082031</v>
       </c>
       <c r="C118" t="n">
         <v>83.69000244140625</v>
@@ -3283,11 +3295,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>67.94387817382812</v>
+        <v>67.94390869140625</v>
       </c>
       <c r="C119" t="n">
         <v>81.56999969482422</v>
@@ -3312,7 +3324,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3341,11 +3353,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>70.62953186035156</v>
+        <v>70.62958526611328</v>
       </c>
       <c r="C121" t="n">
         <v>84.26000213623047</v>
@@ -3370,11 +3382,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>66.30427551269531</v>
+        <v>66.30426788330078</v>
       </c>
       <c r="C122" t="n">
         <v>79.09999847412109</v>
@@ -3399,11 +3411,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>60.77313995361328</v>
+        <v>60.77311706542969</v>
       </c>
       <c r="C123" t="n">
         <v>72</v>
@@ -3428,11 +3440,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>60.78158187866211</v>
+        <v>60.78158569335938</v>
       </c>
       <c r="C124" t="n">
         <v>72.01000213623047</v>
@@ -3457,11 +3469,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>63.7526741027832</v>
+        <v>63.75271224975586</v>
       </c>
       <c r="C125" t="n">
         <v>75.52999877929688</v>
@@ -3486,11 +3498,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>63.75361251831055</v>
+        <v>63.75358963012695</v>
       </c>
       <c r="C126" t="n">
         <v>75.02999877929688</v>
@@ -3515,11 +3527,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>66.91451263427734</v>
+        <v>66.91448211669922</v>
       </c>
       <c r="C127" t="n">
         <v>78.75</v>
@@ -3544,11 +3556,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>70.43229675292969</v>
+        <v>70.43230438232422</v>
       </c>
       <c r="C128" t="n">
         <v>82.88999938964844</v>
@@ -3573,7 +3585,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3602,11 +3614,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>68.63210296630859</v>
+        <v>68.63207244873047</v>
       </c>
       <c r="C130" t="n">
         <v>80.26000213623047</v>
@@ -3631,11 +3643,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>63.14219665527344</v>
+        <v>63.14220809936523</v>
       </c>
       <c r="C131" t="n">
         <v>73.83999633789062</v>
@@ -3660,11 +3672,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>57.77166366577148</v>
+        <v>57.77165222167969</v>
       </c>
       <c r="C132" t="n">
         <v>67.12000274658203</v>
@@ -3689,11 +3701,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>63.30610275268555</v>
+        <v>63.30607223510742</v>
       </c>
       <c r="C133" t="n">
         <v>73.55000305175781</v>
@@ -3718,11 +3730,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>66.30141448974609</v>
+        <v>66.30142974853516</v>
       </c>
       <c r="C134" t="n">
         <v>77.02999877929688</v>
@@ -3747,7 +3759,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -3776,11 +3788,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>72.88251495361328</v>
+        <v>72.88249969482422</v>
       </c>
       <c r="C136" t="n">
         <v>84.11000061035156</v>
@@ -3805,11 +3817,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>71.10613250732422</v>
+        <v>71.10615539550781</v>
       </c>
       <c r="C137" t="n">
         <v>82.05999755859375</v>
@@ -3834,11 +3846,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>69.39375305175781</v>
+        <v>69.39373779296875</v>
       </c>
       <c r="C138" t="n">
         <v>79.56999969482422</v>
@@ -3863,11 +3875,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>71.77462005615234</v>
+        <v>71.77461242675781</v>
       </c>
       <c r="C139" t="n">
         <v>82.30000305175781</v>
@@ -3892,11 +3904,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>72.08855438232422</v>
+        <v>72.08858489990234</v>
       </c>
       <c r="C140" t="n">
         <v>82.66000366210938</v>
@@ -3921,11 +3933,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>71.34593963623047</v>
+        <v>71.34592437744141</v>
       </c>
       <c r="C141" t="n">
         <v>81.29000091552734</v>
@@ -3950,7 +3962,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -3979,11 +3991,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>71.91641998291016</v>
+        <v>71.91642761230469</v>
       </c>
       <c r="C143" t="n">
         <v>81.94000244140625</v>
@@ -4008,11 +4020,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>74.75527954101562</v>
+        <v>74.75526428222656</v>
       </c>
       <c r="C144" t="n">
         <v>84.63999938964844</v>
@@ -4037,11 +4049,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>74.59629058837891</v>
+        <v>74.59632110595703</v>
       </c>
       <c r="C145" t="n">
         <v>84.45999908447266</v>
@@ -4066,11 +4078,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>71.93782806396484</v>
+        <v>71.93780517578125</v>
       </c>
       <c r="C146" t="n">
         <v>81.44999694824219</v>
@@ -4095,11 +4107,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>68.53146362304688</v>
+        <v>68.53144836425781</v>
       </c>
       <c r="C147" t="n">
         <v>77.01999664306641</v>
@@ -4122,7 +4134,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4149,11 +4161,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>72.13507843017578</v>
+        <v>72.13510894775391</v>
       </c>
       <c r="C149" t="n">
         <v>81.06999969482422</v>
@@ -4178,11 +4190,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>76.18933868408203</v>
+        <v>76.18931579589844</v>
       </c>
       <c r="C150" t="n">
         <v>85.04000091552734</v>
@@ -4207,11 +4219,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>76.44915008544922</v>
+        <v>76.44915771484375</v>
       </c>
       <c r="C151" t="n">
         <v>85.33000183105469</v>
@@ -4236,11 +4248,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>88.52619171142578</v>
+        <v>88.52617645263672</v>
       </c>
       <c r="C152" t="n">
         <v>98.80999755859375</v>
@@ -4263,11 +4275,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>95.17738342285156</v>
+        <v>95.17739105224609</v>
       </c>
       <c r="C153" t="n">
         <v>105.6500015258789</v>
@@ -4290,11 +4302,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>96.67282104492188</v>
+        <v>96.67282867431641</v>
       </c>
       <c r="C154" t="n">
         <v>107.3099975585938</v>
@@ -4317,11 +4329,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>97.69082641601562</v>
+        <v>97.69084930419922</v>
       </c>
       <c r="C155" t="n">
         <v>108.4400024414062</v>
@@ -4344,11 +4356,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>107.417854309082</v>
+        <v>107.417839050293</v>
       </c>
       <c r="C156" t="n">
         <v>118.6399993896484</v>
@@ -4373,11 +4385,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>104.774055480957</v>
+        <v>104.774040222168</v>
       </c>
       <c r="C157" t="n">
         <v>115.7200012207031</v>
@@ -4402,11 +4414,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>108.5224456787109</v>
+        <v>108.5224304199219</v>
       </c>
       <c r="C158" t="n">
         <v>119.8600006103516</v>
@@ -4431,11 +4443,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>114.9639663696289</v>
+        <v>114.9639739990234</v>
       </c>
       <c r="C159" t="n">
         <v>126.2900009155273</v>
@@ -4460,11 +4472,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>118.1227645874023</v>
+        <v>118.1227493286133</v>
       </c>
       <c r="C160" t="n">
         <v>129.7599945068359</v>
@@ -4489,11 +4501,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>106.5435180664062</v>
+        <v>106.5435333251953</v>
       </c>
       <c r="C161" t="n">
         <v>117.0400009155273</v>
@@ -4518,11 +4530,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>106.1342697143555</v>
+        <v>106.1342620849609</v>
       </c>
       <c r="C162" t="n">
         <v>115.9400024414062</v>
@@ -4547,11 +4559,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>101.4198532104492</v>
+        <v>101.4198379516602</v>
       </c>
       <c r="C163" t="n">
         <v>110.7900009155273</v>
@@ -4576,7 +4588,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4605,7 +4617,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4634,11 +4646,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>102.9457855224609</v>
+        <v>102.9457778930664</v>
       </c>
       <c r="C166" t="n">
         <v>111.8300018310547</v>
@@ -4663,11 +4675,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>104.897346496582</v>
+        <v>104.8973693847656</v>
       </c>
       <c r="C167" t="n">
         <v>113.9499969482422</v>
@@ -4692,7 +4704,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4721,11 +4733,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>121.6845169067383</v>
+        <v>121.6845397949219</v>
       </c>
       <c r="C169" t="n">
         <v>131.4299926757812</v>
@@ -4750,11 +4762,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>129.2857666015625</v>
+        <v>129.2857208251953</v>
       </c>
       <c r="C170" t="n">
         <v>139.6399993896484</v>
@@ -4779,11 +4791,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>117.3828048706055</v>
+        <v>117.3828125</v>
       </c>
       <c r="C171" t="n">
         <v>126.129997253418</v>
@@ -4808,7 +4820,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4837,11 +4849,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>143.9156188964844</v>
+        <v>143.9156646728516</v>
       </c>
       <c r="C173" t="n">
         <v>154.6399993896484</v>
@@ -4866,7 +4878,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4895,11 +4907,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>153.5133056640625</v>
+        <v>153.5133209228516</v>
       </c>
       <c r="C175" t="n">
         <v>164.1799926757812</v>
@@ -4924,11 +4936,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>140.5257415771484</v>
+        <v>140.5257263183594</v>
       </c>
       <c r="C176" t="n">
         <v>150.2899932861328</v>
@@ -4953,7 +4965,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -4982,11 +4994,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>139.0778961181641</v>
+        <v>139.077880859375</v>
       </c>
       <c r="C178" t="n">
         <v>148.0200042724609</v>
@@ -5011,11 +5023,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>122.5787353515625</v>
+        <v>122.5787200927734</v>
       </c>
       <c r="C179" t="n">
         <v>130.4600067138672</v>
@@ -5040,11 +5052,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>137.55419921875</v>
+        <v>137.5541839599609</v>
       </c>
       <c r="C180" t="n">
         <v>145.6499938964844</v>
@@ -5069,7 +5081,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5098,11 +5110,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>196.4102478027344</v>
+        <v>196.4102172851562</v>
       </c>
       <c r="C182" t="n">
         <v>207.9700012207031</v>
@@ -5127,11 +5139,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>194.3094940185547</v>
+        <v>194.3095092773438</v>
       </c>
       <c r="C183" t="n">
         <v>204.8899993896484</v>
@@ -5156,11 +5168,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>177.1726531982422</v>
+        <v>177.1726379394531</v>
       </c>
       <c r="C184" t="n">
         <v>186.8200073242188</v>
@@ -5185,11 +5197,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>173.331787109375</v>
+        <v>173.3317718505859</v>
       </c>
       <c r="C185" t="n">
         <v>182.7700042724609</v>
@@ -5214,11 +5226,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>190.2625274658203</v>
+        <v>190.2625427246094</v>
       </c>
       <c r="C186" t="n">
         <v>199.7400054931641</v>
@@ -5243,7 +5255,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5272,11 +5284,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>231.9462127685547</v>
+        <v>231.9461822509766</v>
       </c>
       <c r="C188" t="n">
         <v>243.5</v>
@@ -5301,11 +5313,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>246.828857421875</v>
+        <v>246.8287811279297</v>
       </c>
       <c r="C189" t="n">
         <v>258.2900085449219</v>
@@ -5330,11 +5342,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>220.7975311279297</v>
+        <v>220.7975463867188</v>
       </c>
       <c r="C190" t="n">
         <v>231.0500030517578</v>
@@ -5359,7 +5371,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5388,11 +5400,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>237.8032836914062</v>
+        <v>237.8032684326172</v>
       </c>
       <c r="C192" t="n">
         <v>248.0399932861328</v>
@@ -5417,11 +5429,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>264.8203125</v>
+        <v>264.8202514648438</v>
       </c>
       <c r="C193" t="n">
         <v>276.2200012207031</v>
@@ -5446,11 +5458,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>235.2626342773438</v>
+        <v>235.2626647949219</v>
       </c>
       <c r="C194" t="n">
         <v>245.3899993896484</v>
@@ -5475,11 +5487,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>240.6347961425781</v>
+        <v>240.6347808837891</v>
       </c>
       <c r="C195" t="n">
         <v>249.9499969482422</v>
@@ -5504,11 +5516,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>275.6974792480469</v>
+        <v>275.697509765625</v>
       </c>
       <c r="C196" t="n">
         <v>286.3699951171875</v>
@@ -5533,11 +5545,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>281.2428894042969</v>
+        <v>281.2427978515625</v>
       </c>
       <c r="C197" t="n">
         <v>292.1300048828125</v>
@@ -5562,11 +5574,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>302.7754821777344</v>
+        <v>302.7755126953125</v>
       </c>
       <c r="C198" t="n">
         <v>313.4400024414062</v>
@@ -5591,11 +5603,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>313.1983337402344</v>
+        <v>313.1984558105469</v>
       </c>
       <c r="C199" t="n">
         <v>324.2300109863281</v>
@@ -5620,7 +5632,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5649,11 +5661,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>291.9309387207031</v>
+        <v>291.9308471679688</v>
       </c>
       <c r="C201" t="n">
         <v>301.2300109863281</v>
@@ -5678,11 +5690,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>313.3680725097656</v>
+        <v>313.3681030273438</v>
       </c>
       <c r="C202" t="n">
         <v>323.3500061035156</v>
@@ -5707,11 +5719,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>350.9121398925781</v>
+        <v>350.9120788574219</v>
       </c>
       <c r="C203" t="n">
         <v>362.0899963378906</v>
@@ -5736,11 +5748,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>360.6277465820312</v>
+        <v>360.6277160644531</v>
       </c>
       <c r="C204" t="n">
         <v>371.0799865722656</v>
@@ -5765,7 +5777,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5794,7 +5806,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5823,11 +5835,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>303.4324340820312</v>
+        <v>303.4323425292969</v>
       </c>
       <c r="C207" t="n">
         <v>311.2200012207031</v>
@@ -5852,11 +5864,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>334.8266906738281</v>
+        <v>334.8265991210938</v>
       </c>
       <c r="C208" t="n">
         <v>343.4200134277344</v>
@@ -5881,11 +5893,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>385.9544067382812</v>
+        <v>385.9544677734375</v>
       </c>
       <c r="C209" t="n">
         <v>395.8599853515625</v>
@@ -5910,7 +5922,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -5939,11 +5951,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>458.4342041015625</v>
+        <v>458.4341735839844</v>
       </c>
       <c r="C211" t="n">
         <v>468.9800109863281</v>
@@ -5968,11 +5980,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>444.3286437988281</v>
+        <v>444.3285827636719</v>
       </c>
       <c r="C212" t="n">
         <v>454.5499877929688</v>
@@ -5997,11 +6009,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>542.8989868164062</v>
+        <v>542.899169921875</v>
       </c>
       <c r="C213" t="n">
         <v>554.2000122070312</v>
@@ -6026,7 +6038,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6055,11 +6067,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>542.6345825195312</v>
+        <v>542.6344604492188</v>
       </c>
       <c r="C215" t="n">
         <v>553.9299926757812</v>
@@ -6084,11 +6096,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>580.0578002929688</v>
+        <v>580.0577392578125</v>
       </c>
       <c r="C216" t="n">
         <v>591.0399780273438</v>
@@ -6113,11 +6125,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>572.088623046875</v>
+        <v>572.0886840820312</v>
       </c>
       <c r="C217" t="n">
         <v>582.9199829101562</v>
@@ -6142,11 +6154,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>633.6136474609375</v>
+        <v>633.6137084960938</v>
       </c>
       <c r="C218" t="n">
         <v>645.6099853515625</v>
@@ -6171,11 +6183,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>740.97216796875</v>
+        <v>740.9721069335938</v>
       </c>
       <c r="C219" t="n">
         <v>753.6799926757812</v>
@@ -6200,7 +6212,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6229,11 +6241,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>767.9298095703125</v>
+        <v>767.9298706054688</v>
       </c>
       <c r="C221" t="n">
         <v>781.0999755859375</v>
@@ -6258,7 +6270,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6287,11 +6299,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>891.6314697265625</v>
+        <v>891.6315307617188</v>
       </c>
       <c r="C223" t="n">
         <v>905.3800048828125</v>
@@ -6316,7 +6328,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6345,11 +6357,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>946.7628784179688</v>
+        <v>946.7628173828125</v>
       </c>
       <c r="C225" t="n">
         <v>960.02001953125</v>
@@ -6374,11 +6386,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>873.705810546875</v>
+        <v>873.7058715820312</v>
       </c>
       <c r="C226" t="n">
         <v>885.9400024414062</v>
@@ -6403,11 +6415,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>818.2817993164062</v>
+        <v>818.2819213867188</v>
       </c>
       <c r="C227" t="n">
         <v>829.739990234375</v>
@@ -6432,11 +6444,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>785.6658325195312</v>
+        <v>785.6658935546875</v>
       </c>
       <c r="C228" t="n">
         <v>795.3499755859375</v>
@@ -6461,7 +6473,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6490,7 +6502,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6519,11 +6531,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>910.98779296875</v>
+        <v>910.9877319335938</v>
       </c>
       <c r="C231" t="n">
         <v>920.6300048828125</v>
@@ -6548,11 +6560,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>817.259765625</v>
+        <v>817.2597045898438</v>
       </c>
       <c r="C232" t="n">
         <v>825.9099731445312</v>
@@ -6577,7 +6589,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6606,11 +6618,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>731.4402465820312</v>
+        <v>731.440185546875</v>
       </c>
       <c r="C234" t="n">
         <v>737.6699829101562</v>
@@ -6635,7 +6647,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6664,11 +6676,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>733.8200073242188</v>
+        <v>733.8199462890625</v>
       </c>
       <c r="C236" t="n">
         <v>740.0700073242188</v>
@@ -6693,11 +6705,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>727.9887084960938</v>
+        <v>727.9886474609375</v>
       </c>
       <c r="C237" t="n">
         <v>732.5800170898438</v>
@@ -6722,7 +6734,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6751,7 +6763,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6780,7 +6792,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6809,7 +6821,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6838,7 +6850,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6867,7 +6879,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6896,7 +6908,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6925,7 +6937,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6954,7 +6966,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6983,7 +6995,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7012,7 +7024,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7041,7 +7053,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7070,32 +7082,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>1150.989990234375</v>
+        <v>1181.890014648438</v>
       </c>
       <c r="C250" t="n">
-        <v>1150.989990234375</v>
+        <v>1181.890014648438</v>
       </c>
       <c r="D250" t="n">
-        <v>37025900</v>
+        <v>39443600</v>
       </c>
       <c r="E250" t="n">
         <v>29.8</v>
       </c>
       <c r="F250" t="n">
-        <v>38.62382517565017</v>
+        <v>39.66073874659186</v>
       </c>
       <c r="G250" t="n">
         <v>941357065</v>
       </c>
       <c r="H250" t="n">
-        <v>1083492559051.41</v>
+        <v>1112580515342.26</v>
       </c>
       <c r="I250" t="n">
-        <v>0.03933247157389742</v>
+        <v>0.04190078501190194</v>
       </c>
     </row>
   </sheetData>
@@ -7127,75 +7139,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7231,13 +7243,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40753</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7273,13 +7285,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40844</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7315,13 +7327,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40596</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7348,7 +7360,7 @@
       <c r="I5" t="n">
         <v>4.587683351525077</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40844</v>
       </c>
       <c r="K5" t="n">
@@ -7361,13 +7373,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7394,7 +7406,7 @@
       <c r="I6" t="n">
         <v>4.407683351525077</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40844</v>
       </c>
       <c r="K6" t="n">
@@ -7407,13 +7419,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40753</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7440,7 +7452,7 @@
       <c r="I7" t="n">
         <v>4.257683351525078</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40844</v>
       </c>
       <c r="K7" t="n">
@@ -7453,13 +7465,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40844</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7486,7 +7498,7 @@
       <c r="I8" t="n">
         <v>4.187683351525077</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40844</v>
       </c>
       <c r="K8" t="n">
@@ -7499,13 +7511,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7532,7 +7544,7 @@
       <c r="I9" t="n">
         <v>3.9</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="K9" t="n">
@@ -7545,13 +7557,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>41689</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7578,7 +7590,7 @@
       <c r="I10" t="n">
         <v>3.86</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>41689</v>
       </c>
       <c r="K10" t="n">
@@ -7591,13 +7603,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7624,7 +7636,7 @@
       <c r="I11" t="n">
         <v>3.62</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>41689</v>
       </c>
       <c r="K11" t="n">
@@ -7637,13 +7649,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7670,7 +7682,7 @@
       <c r="I12" t="n">
         <v>3.69</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>41689</v>
       </c>
       <c r="K12" t="n">
@@ -7683,13 +7695,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>41689</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7716,7 +7728,7 @@
       <c r="I13" t="n">
         <v>3.66</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>41689</v>
       </c>
       <c r="K13" t="n">
@@ -7729,13 +7741,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41689</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7762,7 +7774,7 @@
       <c r="I14" t="n">
         <v>4.17</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41689</v>
       </c>
       <c r="K14" t="n">
@@ -7775,13 +7787,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7808,7 +7820,7 @@
       <c r="I15" t="n">
         <v>4.45</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41689</v>
       </c>
       <c r="K15" t="n">
@@ -7821,13 +7833,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7854,7 +7866,7 @@
       <c r="I16" t="n">
         <v>4.380000000000001</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41689</v>
       </c>
       <c r="K16" t="n">
@@ -7867,13 +7879,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41689</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7900,7 +7912,7 @@
       <c r="I17" t="n">
         <v>4.31</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41689</v>
       </c>
       <c r="K17" t="n">
@@ -7913,13 +7925,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41757</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7946,7 +7958,7 @@
       <c r="I18" t="n">
         <v>3.57</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41757</v>
       </c>
       <c r="K18" t="n">
@@ -7959,13 +7971,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41848</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7992,7 +8004,7 @@
       <c r="I19" t="n">
         <v>3.14</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41848</v>
       </c>
       <c r="K19" t="n">
@@ -8005,13 +8017,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8038,7 +8050,7 @@
       <c r="I20" t="n">
         <v>2.5</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="K20" t="n">
@@ -8051,13 +8063,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8084,7 +8096,7 @@
       <c r="I21" t="n">
         <v>2.23</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="K21" t="n">
@@ -8097,13 +8109,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8130,7 +8142,7 @@
       <c r="I22" t="n">
         <v>2.05</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="K22" t="n">
@@ -8143,13 +8155,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8176,7 +8188,7 @@
       <c r="I23" t="n">
         <v>1.93</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="K23" t="n">
@@ -8189,13 +8201,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8222,7 +8234,7 @@
       <c r="I24" t="n">
         <v>2.21</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="K24" t="n">
@@ -8235,13 +8247,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8268,7 +8280,7 @@
       <c r="I25" t="n">
         <v>2.26</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="K25" t="n">
@@ -8281,13 +8293,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8314,7 +8326,7 @@
       <c r="I26" t="n">
         <v>2.17</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="K26" t="n">
@@ -8327,13 +8339,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8360,7 +8372,7 @@
       <c r="I27" t="n">
         <v>2.32</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="K27" t="n">
@@ -8373,13 +8385,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8406,7 +8418,7 @@
       <c r="I28" t="n">
         <v>2.3</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="K28" t="n">
@@ -8419,13 +8431,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8452,7 +8464,7 @@
       <c r="I29" t="n">
         <v>2.58</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="K29" t="n">
@@ -8465,13 +8477,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8498,7 +8510,7 @@
       <c r="I30" t="n">
         <v>2.07</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="K30" t="n">
@@ -8511,13 +8523,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8544,7 +8556,7 @@
       <c r="I31" t="n">
         <v>2.31</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="K31" t="n">
@@ -8557,13 +8569,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8590,7 +8602,7 @@
       <c r="I32" t="n">
         <v>2.11</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="K32" t="n">
@@ -8603,13 +8615,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8636,7 +8648,7 @@
       <c r="I33" t="n">
         <v>-0.2000000000000002</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="K33" t="n">
@@ -8649,13 +8661,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8682,7 +8694,7 @@
       <c r="I34" t="n">
         <v>1.06</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="K34" t="n">
@@ -8695,13 +8707,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8728,7 +8740,7 @@
       <c r="I35" t="n">
         <v>-0.1400000000000001</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="K35" t="n">
@@ -8741,13 +8753,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8774,7 +8786,7 @@
       <c r="I36" t="n">
         <v>0.45</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="K36" t="n">
@@ -8787,13 +8799,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43515</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8820,7 +8832,7 @@
       <c r="I37" t="n">
         <v>3.13</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43515</v>
       </c>
       <c r="K37" t="n">
@@ -8833,13 +8845,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8866,7 +8878,7 @@
       <c r="I38" t="n">
         <v>6.279999999999999</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="K38" t="n">
@@ -8879,13 +8891,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8912,7 +8924,7 @@
       <c r="I39" t="n">
         <v>7.970000000000001</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="K39" t="n">
@@ -8925,13 +8937,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8958,7 +8970,7 @@
       <c r="I40" t="n">
         <v>8.220000000000001</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="K40" t="n">
@@ -8971,13 +8983,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43880</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9004,7 +9016,7 @@
       <c r="I41" t="n">
         <v>8.76</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43880</v>
       </c>
       <c r="K41" t="n">
@@ -9017,13 +9029,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9050,7 +9062,7 @@
       <c r="I42" t="n">
         <v>6.05</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="K42" t="n">
@@ -9063,13 +9075,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9096,7 +9108,7 @@
       <c r="I43" t="n">
         <v>6.16</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="K43" t="n">
@@ -9109,13 +9121,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9142,7 +9154,7 @@
       <c r="I44" t="n">
         <v>6.120000000000001</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="K44" t="n">
@@ -9155,13 +9167,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>44244</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9188,7 +9200,7 @@
       <c r="I45" t="n">
         <v>6.789999999999999</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>44244</v>
       </c>
       <c r="K45" t="n">
@@ -9201,13 +9213,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9234,7 +9246,7 @@
       <c r="I46" t="n">
         <v>6.68</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="K46" t="n">
@@ -9247,13 +9259,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9280,7 +9292,7 @@
       <c r="I47" t="n">
         <v>6.659999999999999</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="K47" t="n">
@@ -9293,13 +9305,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9326,7 +9338,7 @@
       <c r="I48" t="n">
         <v>6.55</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="K48" t="n">
@@ -9339,13 +9351,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9372,7 +9384,7 @@
       <c r="I49" t="n">
         <v>6.12</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="K49" t="n">
@@ -9385,13 +9397,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9418,7 +9430,7 @@
       <c r="I50" t="n">
         <v>6.73</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="K50" t="n">
@@ -9431,13 +9443,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9464,7 +9476,7 @@
       <c r="I51" t="n">
         <v>6.25</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="K51" t="n">
@@ -9477,13 +9489,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9510,7 +9522,7 @@
       <c r="I52" t="n">
         <v>6.640000000000001</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="K52" t="n">
@@ -9523,13 +9535,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9556,7 +9568,7 @@
       <c r="I53" t="n">
         <v>6.9</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="K53" t="n">
@@ -9569,13 +9581,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9602,7 +9614,7 @@
       <c r="I54" t="n">
         <v>6.29</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="K54" t="n">
@@ -9615,13 +9627,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>45146</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9648,7 +9660,7 @@
       <c r="I55" t="n">
         <v>7.19</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>45146</v>
       </c>
       <c r="K55" t="n">
@@ -9661,13 +9673,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9694,7 +9706,7 @@
       <c r="I56" t="n">
         <v>5.52</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K56" t="n">
@@ -9707,13 +9719,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9740,7 +9752,7 @@
       <c r="I57" t="n">
         <v>5.8</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="K57" t="n">
@@ -9753,13 +9765,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9786,7 +9798,7 @@
       <c r="I58" t="n">
         <v>6.789999999999999</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="K58" t="n">
@@ -9799,13 +9811,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45512</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9832,7 +9844,7 @@
       <c r="I59" t="n">
         <v>8.120000000000001</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45512</v>
       </c>
       <c r="K59" t="n">
@@ -9845,13 +9857,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9878,7 +9890,7 @@
       <c r="I60" t="n">
         <v>9.249999999999998</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="K60" t="n">
@@ -9891,13 +9903,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9924,7 +9936,7 @@
       <c r="I61" t="n">
         <v>11.71</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="K61" t="n">
@@ -9937,13 +9949,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9970,7 +9982,7 @@
       <c r="I62" t="n">
         <v>12.29</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K62" t="n">
@@ -9983,13 +9995,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10016,7 +10028,7 @@
       <c r="I63" t="n">
         <v>15.3</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="K63" t="n">
@@ -10029,13 +10041,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10062,7 +10074,7 @@
       <c r="I64" t="n">
         <v>20.44</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="K64" t="n">
@@ -10075,13 +10087,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10108,7 +10120,7 @@
       <c r="I65" t="n">
         <v>22.95</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="K65" t="n">
@@ -10121,13 +10133,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10154,7 +10166,7 @@
       <c r="I66" t="n">
         <v>28.15</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="K66" t="n">
@@ -10167,13 +10179,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10200,7 +10212,7 @@
       <c r="I67" t="n">
         <v>29.8</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="K67" t="n">
@@ -10237,52 +10249,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40014</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="C2" t="n">
@@ -10311,10 +10323,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40106</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40116</v>
       </c>
       <c r="C3" t="n">
@@ -10343,10 +10355,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40221</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40231</v>
       </c>
       <c r="C4" t="n">
@@ -10375,10 +10387,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40288</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="C5" t="n">
@@ -10407,10 +10419,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40379</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40392</v>
       </c>
       <c r="C6" t="n">
@@ -10439,10 +10451,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40471</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40480</v>
       </c>
       <c r="C7" t="n">
@@ -10471,10 +10483,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40589</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40596</v>
       </c>
       <c r="C8" t="n">
@@ -10503,10 +10515,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40653</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40662</v>
       </c>
       <c r="C9" t="n">
@@ -10535,10 +10547,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40744</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40753</v>
       </c>
       <c r="C10" t="n">
@@ -10567,10 +10579,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40836</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40844</v>
       </c>
       <c r="C11" t="n">
@@ -10599,10 +10611,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40954</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40963</v>
       </c>
       <c r="C12" t="n">
@@ -10631,10 +10643,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41019</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="C13" t="n">
@@ -10663,10 +10675,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41110</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41117</v>
       </c>
       <c r="C14" t="n">
@@ -10695,10 +10707,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41202</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41208</v>
       </c>
       <c r="C15" t="n">
@@ -10727,10 +10739,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41320</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41326</v>
       </c>
       <c r="C16" t="n">
@@ -10759,10 +10771,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41384</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41390</v>
       </c>
       <c r="C17" t="n">
@@ -10791,10 +10803,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41475</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41481</v>
       </c>
       <c r="C18" t="n">
@@ -10823,10 +10835,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41570</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="C19" t="n">
@@ -10855,10 +10867,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41684</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41689</v>
       </c>
       <c r="C20" t="n">
@@ -10887,10 +10899,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41750</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41757</v>
       </c>
       <c r="C21" t="n">
@@ -10919,10 +10931,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41841</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41848</v>
       </c>
       <c r="C22" t="n">
@@ -10951,10 +10963,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41932</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="C23" t="n">
@@ -10983,10 +10995,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42048</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="C24" t="n">
@@ -11015,10 +11027,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42114</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="C25" t="n">
@@ -11047,10 +11059,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42205</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42215</v>
       </c>
       <c r="C26" t="n">
@@ -11079,10 +11091,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42296</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="C27" t="n">
@@ -11111,10 +11123,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42412</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42419</v>
       </c>
       <c r="C28" t="n">
@@ -11143,10 +11155,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42478</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="C29" t="n">
@@ -11175,10 +11187,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42569</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="C30" t="n">
@@ -11207,10 +11219,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42660</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="C31" t="n">
@@ -11239,10 +11251,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42779</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="C32" t="n">
@@ -11271,10 +11283,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42849</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42856</v>
       </c>
       <c r="C33" t="n">
@@ -11303,10 +11315,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42933</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="C34" t="n">
@@ -11335,10 +11347,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43031</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="C35" t="n">
@@ -11367,10 +11379,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43145</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="C36" t="n">
@@ -11399,10 +11411,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43213</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="C37" t="n">
@@ -11431,10 +11443,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43304</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="C38" t="n">
@@ -11463,10 +11475,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43406</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="C39" t="n">
@@ -11495,10 +11507,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43509</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43515</v>
       </c>
       <c r="C40" t="n">
@@ -11527,10 +11539,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43584</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="C41" t="n">
@@ -11559,10 +11571,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43675</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43679</v>
       </c>
       <c r="C42" t="n">
@@ -11591,10 +11603,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43759</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="C43" t="n">
@@ -11623,10 +11635,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43874</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43880</v>
       </c>
       <c r="C44" t="n">
@@ -11655,10 +11667,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43948</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="C45" t="n">
@@ -11687,10 +11699,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44039</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="C46" t="n">
@@ -11719,10 +11731,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44130</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44132</v>
       </c>
       <c r="C47" t="n">
@@ -11751,10 +11763,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44239</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44244</v>
       </c>
       <c r="C48" t="n">
@@ -11783,10 +11795,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44313</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="C49" t="n">
@@ -11815,10 +11827,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44407</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="C50" t="n">
@@ -11847,10 +11859,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44491</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44496</v>
       </c>
       <c r="C51" t="n">
@@ -11879,10 +11891,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44610</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="C52" t="n">
@@ -11911,10 +11923,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44677</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="C53" t="n">
@@ -11943,10 +11955,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44774</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="C54" t="n">
@@ -11975,10 +11987,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44862</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="C55" t="n">
@@ -12007,10 +12019,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44974</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="C56" t="n">
@@ -12039,10 +12051,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45040</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="C57" t="n">
@@ -12071,10 +12083,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45141</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45146</v>
       </c>
       <c r="C58" t="n">
@@ -12103,10 +12115,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45229</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C59" t="n">
@@ -12135,10 +12147,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45338</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45343</v>
       </c>
       <c r="C60" t="n">
@@ -12167,10 +12179,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45407</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="C61" t="n">
@@ -12199,10 +12211,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45509</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45512</v>
       </c>
       <c r="C62" t="n">
@@ -12231,10 +12243,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45590</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="C63" t="n">
@@ -12263,10 +12275,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45702</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="C64" t="n">
@@ -12295,10 +12307,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45775</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C65" t="n">
@@ -12327,10 +12339,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45873</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="C66" t="n">
@@ -12359,10 +12371,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45957</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45960</v>
       </c>
       <c r="C67" t="n">
@@ -12391,10 +12403,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46062</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="C68" t="n">
@@ -12423,10 +12435,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46139</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="C69" t="n">
@@ -12455,10 +12467,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46237</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46239</v>
       </c>
       <c r="C70" t="n">
@@ -12505,12 +12517,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/LLY.xlsx
+++ b/salidas/empresas/LLY.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>31.53523826599121</v>
+        <v>31.53523063659668</v>
       </c>
       <c r="C2" t="n">
         <v>56.61999893188477</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>31.20042037963867</v>
+        <v>31.20042419433594</v>
       </c>
       <c r="C3" t="n">
         <v>55.61999893188477</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>29.68583869934082</v>
+        <v>29.68585014343262</v>
       </c>
       <c r="C5" t="n">
         <v>52.91999816894531</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>29.19211196899414</v>
+        <v>29.19210624694824</v>
       </c>
       <c r="C6" t="n">
         <v>51.63999938964844</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>31.24416351318359</v>
+        <v>31.24415588378906</v>
       </c>
       <c r="C7" t="n">
         <v>55.27000045776367</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>32.09209442138672</v>
+        <v>32.09210968017578</v>
       </c>
       <c r="C8" t="n">
         <v>56.77000045776367</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>31.84764862060547</v>
+        <v>31.8476505279541</v>
       </c>
       <c r="C9" t="n">
         <v>55.93000030517578</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>32.45691680908203</v>
+        <v>32.45692825317383</v>
       </c>
       <c r="C10" t="n">
         <v>57</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>31.8931999206543</v>
+        <v>31.89321136474609</v>
       </c>
       <c r="C11" t="n">
         <v>56.0099983215332</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>30.74232864379883</v>
+        <v>30.74233245849609</v>
       </c>
       <c r="C12" t="n">
         <v>53.59000015258789</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>29.88758087158203</v>
+        <v>29.8875846862793</v>
       </c>
       <c r="C13" t="n">
         <v>52.09999847412109</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>31.04638290405273</v>
+        <v>31.04636764526367</v>
       </c>
       <c r="C14" t="n">
         <v>54.11999893188477</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>30.40618324279785</v>
+        <v>30.40618515014648</v>
       </c>
       <c r="C15" t="n">
         <v>52.59000015258789</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>31.05374336242676</v>
+        <v>31.05373001098633</v>
       </c>
       <c r="C16" t="n">
         <v>53.70999908447266</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>34.13970947265625</v>
+        <v>34.13972091674805</v>
       </c>
       <c r="C18" t="n">
         <v>58.61999893188477</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>32.54397201538086</v>
+        <v>32.54396438598633</v>
       </c>
       <c r="C19" t="n">
         <v>55.88000106811523</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>31.50147819519043</v>
+        <v>31.50149917602539</v>
       </c>
       <c r="C20" t="n">
         <v>54.09000015258789</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>33.65027618408203</v>
+        <v>33.65027236938477</v>
       </c>
       <c r="C21" t="n">
         <v>57.34999847412109</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>33.40383148193359</v>
+        <v>33.40385055541992</v>
       </c>
       <c r="C22" t="n">
         <v>56.93000030517578</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>31.77266693115234</v>
+        <v>31.77267074584961</v>
       </c>
       <c r="C23" t="n">
         <v>54.15000152587891</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>31.32210731506348</v>
+        <v>31.32214546203613</v>
       </c>
       <c r="C24" t="n">
         <v>52.95000076293945</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>31.58240699768066</v>
+        <v>31.5823974609375</v>
       </c>
       <c r="C25" t="n">
         <v>53.38999938964844</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>29.8640308380127</v>
+        <v>29.86401557922363</v>
       </c>
       <c r="C27" t="n">
         <v>50.02000045776367</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>30.80137825012207</v>
+        <v>30.80136871337891</v>
       </c>
       <c r="C28" t="n">
         <v>51.59000015258789</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>28.74158477783203</v>
+        <v>28.74156951904297</v>
       </c>
       <c r="C29" t="n">
         <v>48.13999938964844</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>29.02132225036621</v>
+        <v>29.02130889892578</v>
       </c>
       <c r="C30" t="n">
         <v>48.13999938964844</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>27.82767868041992</v>
+        <v>27.82766532897949</v>
       </c>
       <c r="C31" t="n">
         <v>46.15999984741211</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>28.3940258026123</v>
+        <v>28.39404106140137</v>
       </c>
       <c r="C33" t="n">
         <v>46.65000152587891</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>26.79933929443359</v>
+        <v>26.79934120178223</v>
       </c>
       <c r="C34" t="n">
         <v>44.02999877929688</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>20.58491325378418</v>
+        <v>20.58491897583008</v>
       </c>
       <c r="C35" t="n">
         <v>33.81999969482422</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>21.077392578125</v>
+        <v>21.07738876342773</v>
       </c>
       <c r="C36" t="n">
         <v>34.15000152587891</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>24.85466766357422</v>
+        <v>24.85466194152832</v>
       </c>
       <c r="C37" t="n">
         <v>40.27000045776367</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>22.72532081604004</v>
+        <v>22.72531890869141</v>
       </c>
       <c r="C38" t="n">
         <v>36.81999969482422</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>18.37711334228516</v>
+        <v>18.37711524963379</v>
       </c>
       <c r="C39" t="n">
         <v>29.3799991607666</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>20.89786911010742</v>
+        <v>20.89786720275879</v>
       </c>
       <c r="C40" t="n">
         <v>33.40999984741211</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>20.59137535095215</v>
+        <v>20.59137916564941</v>
       </c>
       <c r="C41" t="n">
         <v>32.91999816894531</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>21.92266464233398</v>
+        <v>21.92268180847168</v>
       </c>
       <c r="C42" t="n">
         <v>34.56999969482422</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>21.96706390380859</v>
+        <v>21.96706008911133</v>
       </c>
       <c r="C43" t="n">
         <v>34.63999938964844</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>22.12558937072754</v>
+        <v>22.12560653686523</v>
       </c>
       <c r="C44" t="n">
         <v>34.88999938964844</v>
@@ -1346,7 +1346,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>21.25540161132812</v>
+        <v>21.25540351867676</v>
       </c>
       <c r="C46" t="n">
         <v>33.02999877929688</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>21.88605117797852</v>
+        <v>21.88605690002441</v>
       </c>
       <c r="C47" t="n">
         <v>34.0099983215332</v>
@@ -1396,7 +1396,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>23.96894073486328</v>
+        <v>23.96894645690918</v>
       </c>
       <c r="C48" t="n">
         <v>36.72999954223633</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>23.30331993103027</v>
+        <v>23.30332565307617</v>
       </c>
       <c r="C49" t="n">
         <v>35.70999908447266</v>
@@ -1446,7 +1446,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>22.97051620483398</v>
+        <v>22.97051239013672</v>
       </c>
       <c r="C50" t="n">
         <v>35.20000076293945</v>
@@ -1471,7 +1471,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>22.72565460205078</v>
+        <v>22.72564888000488</v>
       </c>
       <c r="C51" t="n">
         <v>34.34000015258789</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>23.14258193969727</v>
+        <v>23.14258575439453</v>
       </c>
       <c r="C53" t="n">
         <v>34.97000122070312</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>22.00551605224609</v>
+        <v>22.00552368164062</v>
       </c>
       <c r="C54" t="n">
         <v>32.79000091552734</v>
@@ -1571,7 +1571,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>22.48200988769531</v>
+        <v>22.48199844360352</v>
       </c>
       <c r="C55" t="n">
         <v>33.5</v>
@@ -1596,7 +1596,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>23.89133071899414</v>
+        <v>23.89132499694824</v>
       </c>
       <c r="C56" t="n">
         <v>35.59999847412109</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>22.83869743347168</v>
+        <v>22.83870506286621</v>
       </c>
       <c r="C57" t="n">
         <v>33.59000015258789</v>
@@ -1646,7 +1646,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>24.83767509460449</v>
+        <v>24.83767700195312</v>
       </c>
       <c r="C58" t="n">
         <v>36.52999877929688</v>
@@ -1696,7 +1696,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>23.20416259765625</v>
+        <v>23.20415306091309</v>
       </c>
       <c r="C60" t="n">
         <v>33.65999984741211</v>
@@ -1746,7 +1746,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>23.96935653686523</v>
+        <v>23.96936225891113</v>
       </c>
       <c r="C62" t="n">
         <v>34.77000045776367</v>
@@ -1771,7 +1771,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>24.15689849853516</v>
+        <v>24.15689468383789</v>
       </c>
       <c r="C63" t="n">
         <v>34.56000137329102</v>
@@ -1796,7 +1796,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>24.58328247070312</v>
+        <v>24.58327484130859</v>
       </c>
       <c r="C64" t="n">
         <v>35.16999816894531</v>
@@ -1821,7 +1821,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>25.86941719055176</v>
+        <v>25.86941528320312</v>
       </c>
       <c r="C65" t="n">
         <v>37.0099983215332</v>
@@ -1846,7 +1846,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>27.24166488647461</v>
+        <v>27.24164772033691</v>
       </c>
       <c r="C66" t="n">
         <v>38.47999954223633</v>
@@ -1871,7 +1871,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>26.56911849975586</v>
+        <v>26.56912040710449</v>
       </c>
       <c r="C67" t="n">
         <v>37.52999877929688</v>
@@ -1896,7 +1896,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>27.11423492431641</v>
+        <v>27.11422538757324</v>
       </c>
       <c r="C68" t="n">
         <v>38.29999923706055</v>
@@ -1921,7 +1921,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>26.93766593933105</v>
+        <v>26.93766403198242</v>
       </c>
       <c r="C69" t="n">
         <v>37.5099983215332</v>
@@ -1971,7 +1971,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>26.68630599975586</v>
+        <v>26.68631362915039</v>
       </c>
       <c r="C71" t="n">
         <v>37.15999984741211</v>
@@ -2000,7 +2000,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>27.53832817077637</v>
+        <v>27.53833389282227</v>
       </c>
       <c r="C72" t="n">
         <v>37.84999847412109</v>
@@ -2029,7 +2029,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>30.23759460449219</v>
+        <v>30.23760795593262</v>
       </c>
       <c r="C73" t="n">
         <v>41.56000137329102</v>
@@ -2058,7 +2058,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>28.91343879699707</v>
+        <v>28.91343688964844</v>
       </c>
       <c r="C74" t="n">
         <v>39.7400016784668</v>
@@ -2087,7 +2087,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>28.91002464294434</v>
+        <v>28.91000747680664</v>
       </c>
       <c r="C75" t="n">
         <v>39.2400016784668</v>
@@ -2116,7 +2116,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>29.66886329650879</v>
+        <v>29.66885566711426</v>
       </c>
       <c r="C76" t="n">
         <v>40.27000045776367</v>
@@ -2145,7 +2145,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>30.4940071105957</v>
+        <v>30.49401664733887</v>
       </c>
       <c r="C77" t="n">
         <v>41.38999938964844</v>
@@ -2174,7 +2174,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>30.52815818786621</v>
+        <v>30.52815055847168</v>
       </c>
       <c r="C78" t="n">
         <v>40.95000076293945</v>
@@ -2203,7 +2203,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>31.98932838439941</v>
+        <v>31.98933029174805</v>
       </c>
       <c r="C79" t="n">
         <v>42.90999984741211</v>
@@ -2232,7 +2232,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>32.82430267333984</v>
+        <v>32.82428741455078</v>
       </c>
       <c r="C80" t="n">
         <v>44.02999877929688</v>
@@ -2261,7 +2261,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>33.86086273193359</v>
+        <v>33.86085891723633</v>
       </c>
       <c r="C81" t="n">
         <v>44.90999984741211</v>
@@ -2290,7 +2290,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>35.74581527709961</v>
+        <v>35.74579238891602</v>
       </c>
       <c r="C82" t="n">
         <v>47.40999984741211</v>
@@ -2369,7 +2369,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>37.56700134277344</v>
+        <v>37.56699752807617</v>
       </c>
       <c r="C85" t="n">
         <v>49.31999969482422</v>
@@ -2394,7 +2394,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>40.89561462402344</v>
+        <v>40.8956298828125</v>
       </c>
       <c r="C86" t="n">
         <v>53.68999862670898</v>
@@ -2419,7 +2419,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>42.01715850830078</v>
+        <v>42.01715087890625</v>
       </c>
       <c r="C87" t="n">
         <v>54.65999984741211</v>
@@ -2444,7 +2444,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>43.65449905395508</v>
+        <v>43.65449142456055</v>
       </c>
       <c r="C88" t="n">
         <v>56.79000091552734</v>
@@ -2469,7 +2469,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>42.57062530517578</v>
+        <v>42.57062149047852</v>
       </c>
       <c r="C89" t="n">
         <v>55.38000106811523</v>
@@ -2494,7 +2494,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>41.2230110168457</v>
+        <v>41.22300720214844</v>
       </c>
       <c r="C90" t="n">
         <v>53.15999984741211</v>
@@ -2519,7 +2519,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>38.09018707275391</v>
+        <v>38.09017181396484</v>
       </c>
       <c r="C91" t="n">
         <v>49.11999893188477</v>
@@ -2569,7 +2569,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>40.22286987304688</v>
+        <v>40.22288131713867</v>
       </c>
       <c r="C93" t="n">
         <v>51.40000152587891</v>
@@ -2594,7 +2594,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>39.38553237915039</v>
+        <v>39.38554382324219</v>
       </c>
       <c r="C94" t="n">
         <v>50.33000183105469</v>
@@ -2644,7 +2644,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>39.68793106079102</v>
+        <v>39.68793487548828</v>
       </c>
       <c r="C96" t="n">
         <v>50.22000122070312</v>
@@ -2669,7 +2669,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>40.30435180664062</v>
+        <v>40.30436325073242</v>
       </c>
       <c r="C97" t="n">
         <v>51</v>
@@ -2694,7 +2694,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>42.68309783935547</v>
+        <v>42.68310928344727</v>
       </c>
       <c r="C98" t="n">
         <v>54.0099983215332</v>
@@ -2719,7 +2719,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>47.53599166870117</v>
+        <v>47.53600311279297</v>
       </c>
       <c r="C99" t="n">
         <v>59.61000061035156</v>
@@ -2748,7 +2748,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>46.93790435791016</v>
+        <v>46.93790054321289</v>
       </c>
       <c r="C100" t="n">
         <v>58.86000061035156</v>
@@ -2777,7 +2777,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>47.12929534912109</v>
+        <v>47.12929153442383</v>
       </c>
       <c r="C101" t="n">
         <v>59.09999847412109</v>
@@ -2806,7 +2806,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>48.13225936889648</v>
+        <v>48.13227081298828</v>
       </c>
       <c r="C102" t="n">
         <v>59.86000061035156</v>
@@ -2835,7 +2835,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>49.98969268798828</v>
+        <v>49.98968124389648</v>
       </c>
       <c r="C103" t="n">
         <v>62.16999816894531</v>
@@ -2864,7 +2864,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>49.09717178344727</v>
+        <v>49.09716796875</v>
       </c>
       <c r="C104" t="n">
         <v>61.06000137329102</v>
@@ -2893,7 +2893,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>51.51869964599609</v>
+        <v>51.51871109008789</v>
       </c>
       <c r="C105" t="n">
         <v>63.56000137329102</v>
@@ -2922,7 +2922,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>52.56430435180664</v>
+        <v>52.56431579589844</v>
       </c>
       <c r="C106" t="n">
         <v>64.84999847412109</v>
@@ -2951,7 +2951,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>53.76394271850586</v>
+        <v>53.763916015625</v>
       </c>
       <c r="C107" t="n">
         <v>66.33000183105469</v>
@@ -2980,7 +2980,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>55.61649322509766</v>
+        <v>55.61647796630859</v>
       </c>
       <c r="C108" t="n">
         <v>68.12000274658203</v>
@@ -3009,7 +3009,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>56.32678985595703</v>
+        <v>56.32678604125977</v>
       </c>
       <c r="C109" t="n">
         <v>68.98999786376953</v>
@@ -3038,7 +3038,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>58.7842903137207</v>
+        <v>58.78429412841797</v>
       </c>
       <c r="C110" t="n">
         <v>72</v>
@@ -3067,7 +3067,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>57.69940185546875</v>
+        <v>57.69941329956055</v>
       </c>
       <c r="C111" t="n">
         <v>70.16999816894531</v>
@@ -3096,7 +3096,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>59.73866271972656</v>
+        <v>59.73868560791016</v>
       </c>
       <c r="C112" t="n">
         <v>72.65000152587891</v>
@@ -3125,7 +3125,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>59.0972900390625</v>
+        <v>59.09730911254883</v>
       </c>
       <c r="C113" t="n">
         <v>71.87000274658203</v>
@@ -3154,7 +3154,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>65.32659149169922</v>
+        <v>65.32659912109375</v>
       </c>
       <c r="C114" t="n">
         <v>78.90000152587891</v>
@@ -3183,7 +3183,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>69.12694549560547</v>
+        <v>69.12696075439453</v>
       </c>
       <c r="C115" t="n">
         <v>83.48999786376953</v>
@@ -3212,7 +3212,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>69.97148132324219</v>
+        <v>69.97150421142578</v>
       </c>
       <c r="C116" t="n">
         <v>84.51000213623047</v>
@@ -3241,7 +3241,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>68.5936279296875</v>
+        <v>68.59363555908203</v>
       </c>
       <c r="C117" t="n">
         <v>82.34999847412109</v>
@@ -3270,7 +3270,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>69.70979309082031</v>
+        <v>69.70977020263672</v>
       </c>
       <c r="C118" t="n">
         <v>83.69000244140625</v>
@@ -3299,7 +3299,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>67.94390869140625</v>
+        <v>67.94393157958984</v>
       </c>
       <c r="C119" t="n">
         <v>81.56999969482422</v>
@@ -3357,7 +3357,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>70.62958526611328</v>
+        <v>70.62955474853516</v>
       </c>
       <c r="C121" t="n">
         <v>84.26000213623047</v>
@@ -3386,7 +3386,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>66.30426788330078</v>
+        <v>66.30426025390625</v>
       </c>
       <c r="C122" t="n">
         <v>79.09999847412109</v>
@@ -3415,7 +3415,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>60.77311706542969</v>
+        <v>60.77312850952148</v>
       </c>
       <c r="C123" t="n">
         <v>72</v>
@@ -3444,7 +3444,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>60.78158569335938</v>
+        <v>60.78157043457031</v>
       </c>
       <c r="C124" t="n">
         <v>72.01000213623047</v>
@@ -3473,7 +3473,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>63.75271224975586</v>
+        <v>63.75269317626953</v>
       </c>
       <c r="C125" t="n">
         <v>75.52999877929688</v>
@@ -3502,7 +3502,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>63.75358963012695</v>
+        <v>63.75358200073242</v>
       </c>
       <c r="C126" t="n">
         <v>75.02999877929688</v>
@@ -3531,7 +3531,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>66.91448211669922</v>
+        <v>66.91451263427734</v>
       </c>
       <c r="C127" t="n">
         <v>78.75</v>
@@ -3560,7 +3560,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>70.43230438232422</v>
+        <v>70.43228912353516</v>
       </c>
       <c r="C128" t="n">
         <v>82.88999938964844</v>
@@ -3589,7 +3589,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>66.48574829101562</v>
+        <v>66.48573303222656</v>
       </c>
       <c r="C129" t="n">
         <v>77.75</v>
@@ -3618,7 +3618,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>68.63207244873047</v>
+        <v>68.63210296630859</v>
       </c>
       <c r="C130" t="n">
         <v>80.26000213623047</v>
@@ -3647,7 +3647,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>63.14220809936523</v>
+        <v>63.1422004699707</v>
       </c>
       <c r="C131" t="n">
         <v>73.83999633789062</v>
@@ -3676,7 +3676,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>57.77165222167969</v>
+        <v>57.77165603637695</v>
       </c>
       <c r="C132" t="n">
         <v>67.12000274658203</v>
@@ -3705,7 +3705,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>63.30607223510742</v>
+        <v>63.30610656738281</v>
       </c>
       <c r="C133" t="n">
         <v>73.55000305175781</v>
@@ -3734,7 +3734,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>66.30142974853516</v>
+        <v>66.30141448974609</v>
       </c>
       <c r="C134" t="n">
         <v>77.02999877929688</v>
@@ -3763,7 +3763,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>71.75602722167969</v>
+        <v>71.75603485107422</v>
       </c>
       <c r="C135" t="n">
         <v>82.80999755859375</v>
@@ -3792,7 +3792,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>72.88249969482422</v>
+        <v>72.88250732421875</v>
       </c>
       <c r="C136" t="n">
         <v>84.11000061035156</v>
@@ -3821,7 +3821,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>71.10615539550781</v>
+        <v>71.10616302490234</v>
       </c>
       <c r="C137" t="n">
         <v>82.05999755859375</v>
@@ -3850,7 +3850,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>69.39373779296875</v>
+        <v>69.39375305175781</v>
       </c>
       <c r="C138" t="n">
         <v>79.56999969482422</v>
@@ -3908,7 +3908,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>72.08858489990234</v>
+        <v>72.08856201171875</v>
       </c>
       <c r="C140" t="n">
         <v>82.66000366210938</v>
@@ -3937,7 +3937,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>71.34592437744141</v>
+        <v>71.34595489501953</v>
       </c>
       <c r="C141" t="n">
         <v>81.29000091552734</v>
@@ -3995,7 +3995,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>71.91642761230469</v>
+        <v>71.91644287109375</v>
       </c>
       <c r="C143" t="n">
         <v>81.94000244140625</v>
@@ -4024,7 +4024,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>74.75526428222656</v>
+        <v>74.75527954101562</v>
       </c>
       <c r="C144" t="n">
         <v>84.63999938964844</v>
@@ -4053,7 +4053,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>74.59632110595703</v>
+        <v>74.59628295898438</v>
       </c>
       <c r="C145" t="n">
         <v>84.45999908447266</v>
@@ -4082,7 +4082,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>71.93780517578125</v>
+        <v>71.93781280517578</v>
       </c>
       <c r="C146" t="n">
         <v>81.44999694824219</v>
@@ -4111,7 +4111,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>68.53144836425781</v>
+        <v>68.53146362304688</v>
       </c>
       <c r="C147" t="n">
         <v>77.01999664306641</v>
@@ -4138,7 +4138,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>68.84288787841797</v>
+        <v>68.84286499023438</v>
       </c>
       <c r="C148" t="n">
         <v>77.37000274658203</v>
@@ -4165,7 +4165,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>72.13510894775391</v>
+        <v>72.13510131835938</v>
       </c>
       <c r="C149" t="n">
         <v>81.06999969482422</v>
@@ -4194,7 +4194,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>76.18931579589844</v>
+        <v>76.1893310546875</v>
       </c>
       <c r="C150" t="n">
         <v>85.04000091552734</v>
@@ -4223,7 +4223,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>76.44915771484375</v>
+        <v>76.44913482666016</v>
       </c>
       <c r="C151" t="n">
         <v>85.33000183105469</v>
@@ -4252,7 +4252,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>88.52617645263672</v>
+        <v>88.52616882324219</v>
       </c>
       <c r="C152" t="n">
         <v>98.80999755859375</v>
@@ -4279,7 +4279,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>95.17739105224609</v>
+        <v>95.17739868164062</v>
       </c>
       <c r="C153" t="n">
         <v>105.6500015258789</v>
@@ -4306,7 +4306,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>96.67282867431641</v>
+        <v>96.67283630371094</v>
       </c>
       <c r="C154" t="n">
         <v>107.3099975585938</v>
@@ -4333,7 +4333,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>97.69084930419922</v>
+        <v>97.69081878662109</v>
       </c>
       <c r="C155" t="n">
         <v>108.4400024414062</v>
@@ -4360,7 +4360,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>107.417839050293</v>
+        <v>107.4178619384766</v>
       </c>
       <c r="C156" t="n">
         <v>118.6399993896484</v>
@@ -4389,7 +4389,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>104.774040222168</v>
+        <v>104.7740478515625</v>
       </c>
       <c r="C157" t="n">
         <v>115.7200012207031</v>
@@ -4418,7 +4418,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>108.5224304199219</v>
+        <v>108.5224533081055</v>
       </c>
       <c r="C158" t="n">
         <v>119.8600006103516</v>
@@ -4447,7 +4447,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>114.9639739990234</v>
+        <v>114.9639587402344</v>
       </c>
       <c r="C159" t="n">
         <v>126.2900009155273</v>
@@ -4476,7 +4476,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>118.1227493286133</v>
+        <v>118.1227645874023</v>
       </c>
       <c r="C160" t="n">
         <v>129.7599945068359</v>
@@ -4505,7 +4505,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>106.5435333251953</v>
+        <v>106.5435485839844</v>
       </c>
       <c r="C161" t="n">
         <v>117.0400009155273</v>
@@ -4534,7 +4534,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>106.1342620849609</v>
+        <v>106.1342697143555</v>
       </c>
       <c r="C162" t="n">
         <v>115.9400024414062</v>
@@ -4563,7 +4563,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>101.4198379516602</v>
+        <v>101.4198303222656</v>
       </c>
       <c r="C163" t="n">
         <v>110.7900009155273</v>
@@ -4592,7 +4592,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>99.73545074462891</v>
+        <v>99.73542022705078</v>
       </c>
       <c r="C164" t="n">
         <v>108.9499969482422</v>
@@ -4621,7 +4621,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>103.9952087402344</v>
+        <v>103.9952011108398</v>
       </c>
       <c r="C165" t="n">
         <v>112.9700012207031</v>
@@ -4650,7 +4650,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>102.9457778930664</v>
+        <v>102.9457931518555</v>
       </c>
       <c r="C166" t="n">
         <v>111.8300018310547</v>
@@ -4679,7 +4679,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>104.8973693847656</v>
+        <v>104.897346496582</v>
       </c>
       <c r="C167" t="n">
         <v>113.9499969482422</v>
@@ -4708,7 +4708,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>108.648551940918</v>
+        <v>108.6485443115234</v>
       </c>
       <c r="C168" t="n">
         <v>117.3499984741211</v>
@@ -4737,7 +4737,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>121.6845397949219</v>
+        <v>121.6845169067383</v>
       </c>
       <c r="C169" t="n">
         <v>131.4299926757812</v>
@@ -4766,7 +4766,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>129.2857208251953</v>
+        <v>129.2857666015625</v>
       </c>
       <c r="C170" t="n">
         <v>139.6399993896484</v>
@@ -4824,7 +4824,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>129.0996704101562</v>
+        <v>129.0996551513672</v>
       </c>
       <c r="C172" t="n">
         <v>138.7200012207031</v>
@@ -4853,7 +4853,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>143.9156646728516</v>
+        <v>143.9156341552734</v>
       </c>
       <c r="C173" t="n">
         <v>154.6399993896484</v>
@@ -4882,7 +4882,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>143.0129089355469</v>
+        <v>143.0129547119141</v>
       </c>
       <c r="C174" t="n">
         <v>152.9499969482422</v>
@@ -4911,7 +4911,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>153.5133209228516</v>
+        <v>153.5133361816406</v>
       </c>
       <c r="C175" t="n">
         <v>164.1799926757812</v>
@@ -4940,7 +4940,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>140.5257263183594</v>
+        <v>140.5257568359375</v>
       </c>
       <c r="C176" t="n">
         <v>150.2899932861328</v>
@@ -4969,7 +4969,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>139.4255065917969</v>
+        <v>139.4254913330078</v>
       </c>
       <c r="C177" t="n">
         <v>148.3899993896484</v>
@@ -4998,7 +4998,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>139.077880859375</v>
+        <v>139.0778656005859</v>
       </c>
       <c r="C178" t="n">
         <v>148.0200042724609</v>
@@ -5027,7 +5027,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>122.5787200927734</v>
+        <v>122.5787048339844</v>
       </c>
       <c r="C179" t="n">
         <v>130.4600067138672</v>
@@ -5056,7 +5056,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>137.5541839599609</v>
+        <v>137.5542144775391</v>
       </c>
       <c r="C180" t="n">
         <v>145.6499938964844</v>
@@ -5085,7 +5085,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>159.4552307128906</v>
+        <v>159.4552154541016</v>
       </c>
       <c r="C181" t="n">
         <v>168.8399963378906</v>
@@ -5143,7 +5143,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>194.3095092773438</v>
+        <v>194.3095245361328</v>
       </c>
       <c r="C183" t="n">
         <v>204.8899993896484</v>
@@ -5201,7 +5201,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>173.3317718505859</v>
+        <v>173.3317565917969</v>
       </c>
       <c r="C185" t="n">
         <v>182.7700042724609</v>
@@ -5230,7 +5230,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>190.2625427246094</v>
+        <v>190.2625579833984</v>
       </c>
       <c r="C186" t="n">
         <v>199.7400054931641</v>
@@ -5317,7 +5317,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>246.8287811279297</v>
+        <v>246.8288116455078</v>
       </c>
       <c r="C189" t="n">
         <v>258.2900085449219</v>
@@ -5346,7 +5346,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>220.7975463867188</v>
+        <v>220.7975311279297</v>
       </c>
       <c r="C190" t="n">
         <v>231.0500030517578</v>
@@ -5375,7 +5375,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>243.4554290771484</v>
+        <v>243.4554595947266</v>
       </c>
       <c r="C191" t="n">
         <v>254.7599945068359</v>
@@ -5433,7 +5433,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>264.8202514648438</v>
+        <v>264.8202819824219</v>
       </c>
       <c r="C193" t="n">
         <v>276.2200012207031</v>
@@ -5462,7 +5462,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>235.2626647949219</v>
+        <v>235.2626495361328</v>
       </c>
       <c r="C194" t="n">
         <v>245.3899993896484</v>
@@ -5491,7 +5491,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>240.6347808837891</v>
+        <v>240.6348114013672</v>
       </c>
       <c r="C195" t="n">
         <v>249.9499969482422</v>
@@ -5520,7 +5520,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>275.697509765625</v>
+        <v>275.6974792480469</v>
       </c>
       <c r="C196" t="n">
         <v>286.3699951171875</v>
@@ -5549,7 +5549,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>281.2427978515625</v>
+        <v>281.2428283691406</v>
       </c>
       <c r="C197" t="n">
         <v>292.1300048828125</v>
@@ -5607,7 +5607,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>313.1984558105469</v>
+        <v>313.1983337402344</v>
       </c>
       <c r="C199" t="n">
         <v>324.2300109863281</v>
@@ -5665,7 +5665,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>291.9308471679688</v>
+        <v>291.9309692382812</v>
       </c>
       <c r="C201" t="n">
         <v>301.2300109863281</v>
@@ -5694,7 +5694,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>313.3681030273438</v>
+        <v>313.3679809570312</v>
       </c>
       <c r="C202" t="n">
         <v>323.3500061035156</v>
@@ -5723,7 +5723,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>350.9120788574219</v>
+        <v>350.9121398925781</v>
       </c>
       <c r="C203" t="n">
         <v>362.0899963378906</v>
@@ -5752,7 +5752,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>360.6277160644531</v>
+        <v>360.6277770996094</v>
       </c>
       <c r="C204" t="n">
         <v>371.0799865722656</v>
@@ -5781,7 +5781,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>355.5353393554688</v>
+        <v>355.535400390625</v>
       </c>
       <c r="C205" t="n">
         <v>365.8399963378906</v>
@@ -5810,7 +5810,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>334.4562683105469</v>
+        <v>334.4563293457031</v>
       </c>
       <c r="C206" t="n">
         <v>344.1499938964844</v>
@@ -5839,7 +5839,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>303.4323425292969</v>
+        <v>303.432373046875</v>
       </c>
       <c r="C207" t="n">
         <v>311.2200012207031</v>
@@ -5868,7 +5868,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>334.8265991210938</v>
+        <v>334.82666015625</v>
       </c>
       <c r="C208" t="n">
         <v>343.4200134277344</v>
@@ -5897,7 +5897,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>385.9544677734375</v>
+        <v>385.9544372558594</v>
       </c>
       <c r="C209" t="n">
         <v>395.8599853515625</v>
@@ -5926,7 +5926,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>419.8028259277344</v>
+        <v>419.8028564453125</v>
       </c>
       <c r="C210" t="n">
         <v>429.4599914550781</v>
@@ -5955,7 +5955,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>458.4341735839844</v>
+        <v>458.4341125488281</v>
       </c>
       <c r="C211" t="n">
         <v>468.9800109863281</v>
@@ -5984,7 +5984,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>444.3285827636719</v>
+        <v>444.3286743164062</v>
       </c>
       <c r="C212" t="n">
         <v>454.5499877929688</v>
@@ -6013,7 +6013,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>542.899169921875</v>
+        <v>542.8991088867188</v>
       </c>
       <c r="C213" t="n">
         <v>554.2000122070312</v>
@@ -6042,7 +6042,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>526.1771850585938</v>
+        <v>526.1771240234375</v>
       </c>
       <c r="C214" t="n">
         <v>537.1300048828125</v>
@@ -6071,7 +6071,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>542.6344604492188</v>
+        <v>542.6345825195312</v>
       </c>
       <c r="C215" t="n">
         <v>553.9299926757812</v>
@@ -6100,7 +6100,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>580.0577392578125</v>
+        <v>580.0575561523438</v>
       </c>
       <c r="C216" t="n">
         <v>591.0399780273438</v>
@@ -6129,7 +6129,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>572.0886840820312</v>
+        <v>572.0885620117188</v>
       </c>
       <c r="C217" t="n">
         <v>582.9199829101562</v>
@@ -6158,7 +6158,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>633.6137084960938</v>
+        <v>633.6136474609375</v>
       </c>
       <c r="C218" t="n">
         <v>645.6099853515625</v>
@@ -6245,7 +6245,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>767.9298706054688</v>
+        <v>767.9298095703125</v>
       </c>
       <c r="C221" t="n">
         <v>781.0999755859375</v>
@@ -6332,7 +6332,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>792.056884765625</v>
+        <v>792.0570068359375</v>
       </c>
       <c r="C224" t="n">
         <v>804.27001953125</v>
@@ -6390,7 +6390,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>873.7058715820312</v>
+        <v>873.7057495117188</v>
       </c>
       <c r="C226" t="n">
         <v>885.9400024414062</v>
@@ -6419,7 +6419,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>818.2819213867188</v>
+        <v>818.2817993164062</v>
       </c>
       <c r="C227" t="n">
         <v>829.739990234375</v>
@@ -6448,7 +6448,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>785.6658935546875</v>
+        <v>785.6658325195312</v>
       </c>
       <c r="C228" t="n">
         <v>795.3499755859375</v>
@@ -6477,7 +6477,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>762.6001586914062</v>
+        <v>762.60009765625</v>
       </c>
       <c r="C229" t="n">
         <v>772</v>
@@ -6506,7 +6506,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>801.204345703125</v>
+        <v>801.2044067382812</v>
       </c>
       <c r="C230" t="n">
         <v>811.0800170898438</v>
@@ -6535,7 +6535,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>910.9877319335938</v>
+        <v>910.9876708984375</v>
       </c>
       <c r="C231" t="n">
         <v>920.6300048828125</v>
@@ -6564,7 +6564,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>817.2597045898438</v>
+        <v>817.2598266601562</v>
       </c>
       <c r="C232" t="n">
         <v>825.9099731445312</v>
@@ -6622,7 +6622,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>731.440185546875</v>
+        <v>731.4401245117188</v>
       </c>
       <c r="C234" t="n">
         <v>737.6699829101562</v>
@@ -6854,7 +6854,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>1032.163452148438</v>
+        <v>1032.163330078125</v>
       </c>
       <c r="C242" t="n">
         <v>1037.150024414062</v>
